--- a/data/trans_camb/P42-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P42-Habitat-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,97</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,53</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,53</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,97</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8,0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6,53</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,0; 14,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,83; 12,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,99; 11,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 15,28</t>
+          <t>7,0; 14,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 12,27</t>
+          <t>3,83; 12,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 11,24</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,9; 15,28</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3,46; 12,27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2,09; 11,24</t>
+          <t>1,99; 11,04</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,69%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8,75%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,05; 20,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,95; 17,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,56; 15,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 21,28</t>
+          <t>9,05; 20,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 16,96</t>
+          <t>4,95; 17,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,53</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,0; 21,28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4,48; 16,96</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2,7; 15,53</t>
+          <t>2,56; 15,18</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,32</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,5</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,88</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10,32</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6,5</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,45; 10,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,9; 14,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,92; 10,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 10,31</t>
+          <t>3,45; 10,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 13,53</t>
+          <t>6,9; 14,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,3</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,29; 10,31</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 13,53</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2,23; 10,3</t>
+          <t>2,92; 10,52</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8,33%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,22; 13,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,81; 18,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,66; 13,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 13,75</t>
+          <t>4,22; 13,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,55; 17,86</t>
+          <t>8,81; 18,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 13,48</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,14; 13,75</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8,55; 17,86</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2,81; 13,48</t>
+          <t>3,66; 13,74</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18,69</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-18,69</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,73</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3,67</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>-18,69</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,17; 10,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,02; 7,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-52,88; 7,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 10,37</t>
+          <t>3,17; 10,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 7,49</t>
+          <t>0,02; 7,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 7,67</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,36; 10,37</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-0,19; 7,49</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-55,59; 7,67</t>
+          <t>-52,88; 7,94</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-22,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-22,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>-22,45%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,79; 12,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,12; 8,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-63,9; 9,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,82</t>
+          <t>3,79; 12,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 9,06</t>
+          <t>0,12; 8,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,86; 9,32</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>3,92; 12,82</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-0,26; 9,06</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-66,86; 9,32</t>
+          <t>-63,9; 9,5</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,84</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,46</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8,84</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3,46</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,15; 11,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,79; 11,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,5; 8,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 11,01</t>
+          <t>5,15; 11,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,7; 12,28</t>
+          <t>5,79; 11,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 7,94</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,67; 11,01</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5,7; 12,28</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-0,6; 7,94</t>
+          <t>-0,5; 8,35</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4,31%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,22; 14,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,05; 15,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,62; 10,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,62; 14,11</t>
+          <t>6,22; 14,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,89; 15,74</t>
+          <t>7,05; 15,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 10,07</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,62; 14,11</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6,89; 15,74</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; 10,07</t>
+          <t>-0,62; 10,52</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,05</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,08</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8,05</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>8,08</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>-0,56</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,18; 9,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,17; 9,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,73; 6,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,98</t>
+          <t>6,18; 9,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,93</t>
+          <t>6,17; 9,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 6,21</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>6,43; 9,98</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>6,4; 9,93</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-19,42; 6,21</t>
+          <t>-17,73; 6,29</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,71%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-0,71%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>-0,71%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,63; 12,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,69; 12,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,6; 8,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,86</t>
+          <t>7,63; 12,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,81</t>
+          <t>7,69; 12,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 7,89</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>8,02; 12,86</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>8,01; 12,81</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>-24,65; 7,89</t>
+          <t>-22,6; 8,01</t>
         </is>
       </c>
     </row>
@@ -1699,13 +1371,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A19"/>

--- a/data/trans_camb/P42-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P42-Habitat-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>6,13</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 14,97</t>
+          <t>6,79; 14,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 12,48</t>
+          <t>3,65; 12,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 11,04</t>
+          <t>1,77; 10,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 14,97</t>
+          <t>6,79; 14,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 12,48</t>
+          <t>3,65; 12,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 11,04</t>
+          <t>1,77; 10,82</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 20,82</t>
+          <t>8,83; 20,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 17,25</t>
+          <t>4,8; 17,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 15,18</t>
+          <t>2,28; 14,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 20,82</t>
+          <t>8,83; 20,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 17,25</t>
+          <t>4,8; 17,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 15,18</t>
+          <t>2,28; 14,95</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>6,48</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>6,48</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,42</t>
+          <t>3,31; 10,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 14,03</t>
+          <t>7,19; 14,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 10,52</t>
+          <t>2,41; 10,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,42</t>
+          <t>3,31; 10,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 14,03</t>
+          <t>7,19; 14,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 10,52</t>
+          <t>2,41; 10,12</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 13,77</t>
+          <t>4,07; 13,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 18,62</t>
+          <t>8,97; 18,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 13,74</t>
+          <t>3,0; 13,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 13,77</t>
+          <t>4,07; 13,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 18,62</t>
+          <t>8,97; 18,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 13,74</t>
+          <t>3,0; 13,36</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-18,69</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-18,69</t>
+          <t>5,55</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,47</t>
+          <t>3,45; 10,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,29</t>
+          <t>-0,03; 7,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 7,94</t>
+          <t>1,21; 9,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,47</t>
+          <t>3,45; 10,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,29</t>
+          <t>-0,03; 7,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 7,94</t>
+          <t>1,21; 9,35</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-22,45%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-22,45%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 12,96</t>
+          <t>4,01; 12,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,98</t>
+          <t>0,01; 9,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-63,9; 9,5</t>
+          <t>1,42; 11,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 12,96</t>
+          <t>4,01; 12,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,98</t>
+          <t>0,01; 9,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,9; 9,5</t>
+          <t>1,42; 11,49</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>1,1</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,55</t>
+          <t>4,63; 11,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,87</t>
+          <t>5,48; 11,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 8,35</t>
+          <t>-2,78; 4,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,55</t>
+          <t>4,63; 11,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,87</t>
+          <t>5,48; 11,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 8,35</t>
+          <t>-2,78; 4,89</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,22; 14,55</t>
+          <t>5,6; 14,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,05; 15,15</t>
+          <t>6,68; 15,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 10,52</t>
+          <t>-3,41; 6,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,22; 14,55</t>
+          <t>5,6; 14,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,05; 15,15</t>
+          <t>6,68; 15,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 10,52</t>
+          <t>-3,41; 6,2</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>4,6</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,9</t>
+          <t>6,34; 9,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,88</t>
+          <t>6,38; 9,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 6,29</t>
+          <t>2,75; 6,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,9</t>
+          <t>6,34; 9,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,88</t>
+          <t>6,38; 9,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 6,29</t>
+          <t>2,75; 6,73</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-0,71%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,71%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,72</t>
+          <t>7,86; 12,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,62</t>
+          <t>7,94; 12,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 8,01</t>
+          <t>3,46; 8,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,72</t>
+          <t>7,86; 12,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,62</t>
+          <t>7,94; 12,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 8,01</t>
+          <t>3,46; 8,63</t>
         </is>
       </c>
     </row>
